--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4722,6 +4722,131 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>113457727</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97314</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Farligkärrshöjden, NV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>463140</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6589670</v>
+      </c>
+      <c r="S36" t="n">
+        <v>64</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>S-Sto-0075</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>11 dellokaler inom polygonen med 7 - 250 skott/dellokal. Rikligast i söder, väst och nordväst. För detaljer se allmänna artportalen.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Frida Afzelius, Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -4727,7 +4727,7 @@
         <v>113457727</v>
       </c>
       <c r="B36" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4847,6 +4847,466 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114929286</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bjurtjärn (Bjurtjärn), Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>463031</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6589875</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114928639</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bjurtjärn (Bjurtjärn), Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>463002</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6589877</v>
+      </c>
+      <c r="S38" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114928786</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bjurtjärn (Bjurtjärn), Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>463009</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6589879</v>
+      </c>
+      <c r="S39" t="n">
+        <v>14</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>114934541</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>463061</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6589897</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Satt i toppen av en klen torraka. Lite långt håll och inte bästa ljuset men den hade inget rött på buken och precis när den flög iväg tittade den till mot oss och dess gula hjässa syntes tydligt. Vi såg ca 25 tallar med drickringar av varierande ålder från koordinaten och ca 350 m söderut öster om reservatet.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Gammal blandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21083-2023 artfynd.xlsx
+++ b/artfynd/A 21083-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5307,6 +5307,1593 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>114940393</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>463102</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6589823</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tall med drickringar</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>114940391</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>463048</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6589737</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tre närstående tallar med drickringar av varierande ålder</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>114940450</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>463054</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6589865</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tall med drickringar</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114940392</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>463065</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6589751</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Tall med drickringar</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>114940390</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>463059</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6589711</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tall med drickringar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>114941315</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fattigkärrshöjden, NV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>463146</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6589633</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 500 skott i två ungefär jämnstora grupper strax öster om surdeåget/smala mossen. Den ena ett par meter väster om en stor tall med en massa hackspetthack i. Den andra ca 10 öster om tallen högre upp i sluttningen.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>114940394</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>463092</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6589856</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Tall med drickringar</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>114940389</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fattigkärrshöjden, NV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>463082</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6589690</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Tall med drickringar</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>114940386</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fattigkärrshöjden, NV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>463146</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6589633</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Grov tall med rikligt av cm-djupa hackmärken.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>114940388</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fattigkärrshöjden, VNV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>463084</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6589553</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tre närstående tallar med drickringar, den ena troligen från våren 2023</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>114940387</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fattigkärrshöjden, VNV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>463030</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6589520</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Två närstående tallar med drickringar</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Äldre blandbarrskog, gammal naturskog.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>114941127</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fattigkärrshöjden, VNV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>463061</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6589602</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Owe Nilsson, Therese Steiner, Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>114940699</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4760</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fridenborgshöjden, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>463054</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6589859</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bjurtjärn</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Något år gamla gnag och kläckhål i gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
